--- a/orders.xlsx
+++ b/orders.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1051,6 +1051,118 @@
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ORD202511020046071617</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-02 00:46:07</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>LAPTOP</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>796694820003872</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>[{"title": "Unnamed Product", "quantity": 1, "price": 385.0, "item_total": 385.0, "retailer_id": "i6s3jodpvd"}]</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ORD202511020144071617</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-02 01:44:07</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>263776681617</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Codeconel👨‍💻</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LAPTOP</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>390</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>796694820003872</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>[{"title": "Unnamed Product", "quantity": 1, "price": 390.0, "item_total": 390.0, "retailer_id": "i6s3jodpvd"}]</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
